--- a/Docs/Test-Report/Bug_Report.xlsx
+++ b/Docs/Test-Report/Bug_Report.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KiemChungPhanMem\Docs\Test-Report\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C51A0B6A-F0D6-42FB-AC8E-5A2F92EE716F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,10 +24,97 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+  <si>
+    <t>Bug ID</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>API Endpoint</t>
+  </si>
+  <si>
+    <t>Title (Tiêu đề Bug)</t>
+  </si>
+  <si>
+    <t>Severity (Mức độ)</t>
+  </si>
+  <si>
+    <t>Priority (Ưu tiên)</t>
+  </si>
+  <si>
+    <t>Expected Result (Kỳ vọng)</t>
+  </si>
+  <si>
+    <t>Actual Result (Thực tế)</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>BUG_API_002</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>POST /api/seller/product/new</t>
+  </si>
+  <si>
+    <t>[API] Lỗi 500 do lỗi Serialize JSON (Jackson) khi bắt lỗi Validate dữ liệu thêm mới Sản phẩm</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>BUG_API_003</t>
+  </si>
+  <si>
+    <t>Order</t>
+  </si>
+  <si>
+    <t>[API] Lỗi 500 và sai chính tả ("is not exit!") khi thao tác với ID Đơn hàng không tồn tại</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Trả về 400 Bad Request kèm thông báo lỗi Validate cụ thể cho các field nhập sai.</t>
+  </si>
+  <si>
+    <t>Trả về 500 Internal Server Error kèm lỗi No serializer found for class... DefaultMessageCodesResolver.</t>
+  </si>
+  <si>
+    <t>Trả về 404 Not Found (hoặc 400) kèm câu thông báo chuẩn: "Order does not exist" hoặc "Order not found".</t>
+  </si>
+  <si>
+    <t>Trả về 500 Internal Server Error kèm câu thông báo sai chính tả: "OrderMain is not exit!".</t>
+  </si>
+  <si>
+    <t>GET /api/order/{id} 
+PATCH /api/order/cancel/{id} 
+PATCH /api/order/finish/{id}</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -37,7 +130,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +138,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +450,108 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.109375" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" customWidth="1"/>
+    <col min="7" max="7" width="23" customWidth="1"/>
+    <col min="8" max="8" width="22.21875" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Docs/Test-Report/Bug_Report.xlsx
+++ b/Docs/Test-Report/Bug_Report.xlsx
@@ -1,111 +1,354 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20398"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KiemChungPhanMem\Docs\Test-Report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C51A0B6A-F0D6-42FB-AC8E-5A2F92EE716F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2735BCE-9677-48A1-A8B9-1EC690CA1772}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="HƯỚNG DẪN" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="107">
   <si>
     <t>Bug ID</t>
   </si>
   <si>
-    <t>Module</t>
-  </si>
-  <si>
-    <t>API Endpoint</t>
-  </si>
-  <si>
-    <t>Title (Tiêu đề Bug)</t>
-  </si>
-  <si>
-    <t>Severity (Mức độ)</t>
-  </si>
-  <si>
-    <t>Priority (Ưu tiên)</t>
-  </si>
-  <si>
-    <t>Expected Result (Kỳ vọng)</t>
-  </si>
-  <si>
-    <t>Actual Result (Thực tế)</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>BUG_API_002</t>
-  </si>
-  <si>
-    <t>Product</t>
-  </si>
-  <si>
-    <t>POST /api/seller/product/new</t>
-  </si>
-  <si>
-    <t>[API] Lỗi 500 do lỗi Serialize JSON (Jackson) khi bắt lỗi Validate dữ liệu thêm mới Sản phẩm</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>Open</t>
-  </si>
-  <si>
-    <t>BUG_API_003</t>
-  </si>
-  <si>
-    <t>Order</t>
-  </si>
-  <si>
-    <t>[API] Lỗi 500 và sai chính tả ("is not exit!") khi thao tác với ID Đơn hàng không tồn tại</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>Trả về 400 Bad Request kèm thông báo lỗi Validate cụ thể cho các field nhập sai.</t>
-  </si>
-  <si>
-    <t>Trả về 500 Internal Server Error kèm lỗi No serializer found for class... DefaultMessageCodesResolver.</t>
-  </si>
-  <si>
-    <t>Trả về 404 Not Found (hoặc 400) kèm câu thông báo chuẩn: "Order does not exist" hoặc "Order not found".</t>
-  </si>
-  <si>
-    <t>Trả về 500 Internal Server Error kèm câu thông báo sai chính tả: "OrderMain is not exit!".</t>
-  </si>
-  <si>
-    <t>GET /api/order/{id} 
-PATCH /api/order/cancel/{id} 
-PATCH /api/order/finish/{id}</t>
+    <t>Tiêu đề</t>
+  </si>
+  <si>
+    <t>Endpoint / Màn hình</t>
+  </si>
+  <si>
+    <t>Test Case liên quan</t>
+  </si>
+  <si>
+    <t>Steps to Reproduce</t>
+  </si>
+  <si>
+    <t>Expected</t>
+  </si>
+  <si>
+    <t>Actual</t>
+  </si>
+  <si>
+    <t>Mức độ</t>
+  </si>
+  <si>
+    <t>Jira Status</t>
+  </si>
+  <si>
+    <t>Người tìm</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>BUG-01</t>
+  </si>
+  <si>
+    <t>Đăng ký với role tự chọn (Lỗ hổng leo thang đặc quyền)</t>
+  </si>
+  <si>
+    <t>POST /register</t>
+  </si>
+  <si>
+    <t>TC-AUTH-01</t>
+  </si>
+  <si>
+    <t>Gửi POST /register với Body có "role": "ROLE_MANAGER"</t>
+  </si>
+  <si>
+    <t>Hệ thống từ chối hoặc ép role về CUSTOMER</t>
+  </si>
+  <si>
+    <t>Hệ thống chấp nhận role do client gửi - tự đăng ký thành Manager</t>
+  </si>
+  <si>
+    <t>Cao (Security)</t>
+  </si>
+  <si>
+    <t>To Do</t>
+  </si>
+  <si>
+    <t>Root cause: UserController.save() không sanitize field role</t>
+  </si>
+  <si>
+    <t>BUG-02</t>
+  </si>
+  <si>
+    <t>Đăng ký email trùng trả 500 thay vì 400</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_REG_02</t>
+  </si>
+  <si>
+    <t>Đăng ký 2 lần với cùng 1 email</t>
+  </si>
+  <si>
+    <t>400 Bad Request</t>
+  </si>
+  <si>
+    <t>500 Internal Server Error</t>
+  </si>
+  <si>
+    <t>Trung bình</t>
+  </si>
+  <si>
+    <t>Root cause: exception xảy ra sau thời điểm try-catch do Hibernate deferred flush</t>
+  </si>
+  <si>
+    <t>BUG-03</t>
+  </si>
+  <si>
+    <t>Tạo sản phẩm trùng ID trả 500 thay vì 400</t>
+  </si>
+  <si>
+    <t>POST /seller/product/new</t>
+  </si>
+  <si>
+    <t>TC-AUTH-26 (case trùng ID)</t>
+  </si>
+  <si>
+    <t>Tạo sản phẩm với productId đã tồn tại (vd B0001)</t>
+  </si>
+  <si>
+    <t>Root cause: trả thẳng object BindingResult làm response body, Jackson không serialize được</t>
+  </si>
+  <si>
+    <t>BUG-04</t>
+  </si>
+  <si>
+    <t>Sửa sản phẩm lỗi validate trả 500 thay vì 400</t>
+  </si>
+  <si>
+    <t>PUT /seller/product/{id}/edit</t>
+  </si>
+  <si>
+    <t>TC-AUTH-24/25</t>
+  </si>
+  <si>
+    <t>Gửi PUT edit với dữ liệu thiếu field bắt buộc</t>
+  </si>
+  <si>
+    <t>500 Internal Server Error (nghi ngờ, cùng root cause BUG-03)</t>
+  </si>
+  <si>
+    <t>Cùng nguyên nhân BindingResult như BUG-03, cần test xác nhận thực tế</t>
+  </si>
+  <si>
+    <t>BUG-05</t>
+  </si>
+  <si>
+    <t>Xóa sản phẩm ID không tồn tại có nguy cơ 500</t>
+  </si>
+  <si>
+    <t>DELETE /seller/product/{id}/delete</t>
+  </si>
+  <si>
+    <t>TC-AUTH-27</t>
+  </si>
+  <si>
+    <t>Gọi DELETE với id không tồn tại trong DB</t>
+  </si>
+  <si>
+    <t>400 hoặc 404</t>
+  </si>
+  <si>
+    <t>Nghi ngờ 500 (chưa test xác nhận - không có try-catch trong code)</t>
+  </si>
+  <si>
+    <t>Thấp</t>
+  </si>
+  <si>
+    <t>Suy luận từ code, cần Execute Tuần 2 để xác nhận</t>
+  </si>
+  <si>
+    <t>BUG-06</t>
+  </si>
+  <si>
+    <t>Gọi finish lần 2 trên đơn đã hoàn tất trả 500</t>
+  </si>
+  <si>
+    <t>PATCH /order/finish/{id}</t>
+  </si>
+  <si>
+    <t>TC-AUTH-29/30</t>
+  </si>
+  <si>
+    <t>Gọi finish 1 đơn hàng đã ở trạng thái Completed</t>
+  </si>
+  <si>
+    <t>400 Bad Request (đơn đã hoàn tất)</t>
+  </si>
+  <si>
+    <t>Root cause: OrderController không check null/trạng thái trước khi update - đã xác nhận qua test thật</t>
+  </si>
+  <si>
+    <t>BUG-07</t>
+  </si>
+  <si>
+    <t>Xem/hủy đơn hàng ID không tồn tại gây NullPointerException</t>
+  </si>
+  <si>
+    <t>GET/PATCH /order/{id}</t>
+  </si>
+  <si>
+    <t>TC-AUTH-15/16</t>
+  </si>
+  <si>
+    <t>Gọi GET hoặc PATCH cancel với id không tồn tại</t>
+  </si>
+  <si>
+    <t>404 Not Found</t>
+  </si>
+  <si>
+    <t>500 Internal Server Error (NullPointerException)</t>
+  </si>
+  <si>
+    <t>Root cause: orderService.findOne() trả null, code gọi .getBuyerEmail() ngay sau không check null</t>
+  </si>
+  <si>
+    <t>BUG-08</t>
+  </si>
+  <si>
+    <t>Xem sản phẩm theo danh mục type không hợp lệ có nguy cơ 500</t>
+  </si>
+  <si>
+    <t>GET /category/{type}</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Gọi GET /category/{type} với type không tồn tại</t>
+  </si>
+  <si>
+    <t>Suy luận từ code, chưa có Test Case chính thức - cần bổ sung</t>
+  </si>
+  <si>
+    <t>BUG-09</t>
+  </si>
+  <si>
+    <t>Checkout khi hết hàng có nguy cơ 500</t>
+  </si>
+  <si>
+    <t>POST /cart/checkout</t>
+  </si>
+  <si>
+    <t>TC_FE_CUS_CHK_02</t>
+  </si>
+  <si>
+    <t>Checkout khi sản phẩm trong giỏ không đủ tồn kho</t>
+  </si>
+  <si>
+    <t>400 Bad Request (hết hàng)</t>
+  </si>
+  <si>
+    <t>BUG-EMP-01</t>
+  </si>
+  <si>
+    <t>Sửa sản phẩm cho phép nhập giá âm (role Employee)</t>
+  </si>
+  <si>
+    <t>PUT /seller/product/{id}/edit (UI)</t>
+  </si>
+  <si>
+    <t>TC_FE_EMP_03</t>
+  </si>
+  <si>
+    <t>Đăng nhập Employee, sửa productPrice = -10, bấm Save</t>
+  </si>
+  <si>
+    <t>Không cho lưu, hiển thị lỗi validate</t>
+  </si>
+  <si>
+    <t>Lưu thành công, giá âm được chấp nhận</t>
+  </si>
+  <si>
+    <t>Cao</t>
+  </si>
+  <si>
+    <t>Đã xác nhận qua Entity: ProductInfo.productPrice không có @Min/@Positive</t>
+  </si>
+  <si>
+    <t>BUG-MGR-01</t>
+  </si>
+  <si>
+    <t>Sửa sản phẩm cho phép nhập giá âm (role Manager)</t>
+  </si>
+  <si>
+    <t>TC_FE_MGR_03</t>
+  </si>
+  <si>
+    <t>Đăng nhập Manager, sửa productPrice = -10, bấm Save</t>
+  </si>
+  <si>
+    <t>Cùng root cause BUG-EMP-01, dùng chung form Edit Product</t>
+  </si>
+  <si>
+    <t>HƯỚNG DẪN DÙNG FILE NÀY</t>
+  </si>
+  <si>
+    <t>10 Bug đầu tiên đã được điền sẵn (BUG-01 -&gt; BUG-MGR-01) - đây là các bug</t>
+  </si>
+  <si>
+    <t>đã phân tích/phát hiện được từ trước, dựa trên source code thật.</t>
+  </si>
+  <si>
+    <t>Việc nhóm cần làm ở Tuần 2:</t>
+  </si>
+  <si>
+    <t>1. Với mỗi Bug đã điền sẵn: TẠO TICKET THẬT trên Jira (copy nội dung từ file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   này), sau đó quay lại điền mã Jira ticket vào cột 'Jira Status'.</t>
+  </si>
+  <si>
+    <t>2. Khi Execute Test Case phát sinh Bug MỚI (ngoài 10 bug đã biết): thêm dòng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   mới vào cuối file này, đặt Bug ID tiếp theo (BUG-10, BUG-11...).</t>
+  </si>
+  <si>
+    <t>3. Cột 'Người tìm': ghi theo assignee của Test Case tương ứng (xem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Test_Execution_Report_FE.xlsx / API.xlsx để biết ai Execute case nào).</t>
+  </si>
+  <si>
+    <t>4. Cột 'Người Fix (Tuần 3)': để trống ở Tuần 2, chỉ điền khi qua Tuần 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   (Fix Bug) đã phân công xong ai fix bug nào.</t>
+  </si>
+  <si>
+    <t>5. Cột 'Mức độ': Cao (ảnh hưởng bảo mật/dữ liệu) / Trung bình (lỗi rõ ràng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   nhưng có thể workaround) / Thấp (edge case hiếm gặp).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Người Fix </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,18 +359,34 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor rgb="FFC00000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -140,16 +399,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FFB0B0B0"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FFB0B0B0"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FFB0B0B0"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FFB0B0B0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -159,24 +418,20 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -199,44 +454,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -263,15 +518,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -298,7 +552,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -310,160 +563,187 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23" customWidth="1"/>
-    <col min="8" max="8" width="22.21875" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="36" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
+    <col min="8" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -491,67 +771,480 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="K1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="3" t="s">
+    </row>
+    <row r="2" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="D3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>14</v>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:A16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="90" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Docs/Test-Report/Bug_Report.xlsx
+++ b/Docs/Test-Report/Bug_Report.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\New folder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\moi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2735BCE-9677-48A1-A8B9-1EC690CA1772}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00D5DFC7-30F0-471C-BF8B-46EDFE26D237}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23490" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="126">
   <si>
     <t>Bug ID</t>
   </si>
@@ -83,6 +83,9 @@
     <t>To Do</t>
   </si>
   <si>
+    <t>E</t>
+  </si>
+  <si>
     <t>Root cause: UserController.save() không sanitize field role</t>
   </si>
   <si>
@@ -107,6 +110,9 @@
     <t>Trung bình</t>
   </si>
   <si>
+    <t>C</t>
+  </si>
+  <si>
     <t>Root cause: exception xảy ra sau thời điểm try-catch do Hibernate deferred flush</t>
   </si>
   <si>
@@ -125,7 +131,7 @@
     <t>Tạo sản phẩm với productId đã tồn tại (vd B0001)</t>
   </si>
   <si>
-    <t>Root cause: trả thẳng object BindingResult làm response body, Jackson không serialize được</t>
+    <t>Root cause: trả thẳng object BindingResult làm response body, Jackson không serialize được | Xác nhận thêm qua TC_API_BVA_05 (productStock=-1 khi tạo SP mới cũng trả 500, cùng root cause BindingResult).</t>
   </si>
   <si>
     <t>BUG-04</t>
@@ -257,9 +263,6 @@
     <t>400 Bad Request (hết hàng)</t>
   </si>
   <si>
-    <t>BUG-EMP-01</t>
-  </si>
-  <si>
     <t>Sửa sản phẩm cho phép nhập giá âm (role Employee)</t>
   </si>
   <si>
@@ -269,9 +272,6 @@
     <t>TC_FE_EMP_03</t>
   </si>
   <si>
-    <t>Đăng nhập Employee, sửa productPrice = -10, bấm Save</t>
-  </si>
-  <si>
     <t>Không cho lưu, hiển thị lỗi validate</t>
   </si>
   <si>
@@ -281,10 +281,7 @@
     <t>Cao</t>
   </si>
   <si>
-    <t>Đã xác nhận qua Entity: ProductInfo.productPrice không có @Min/@Positive</t>
-  </si>
-  <si>
-    <t>BUG-MGR-01</t>
+    <t>Đã xác nhận qua Entity: ProductInfo.productPrice không có @Min/@Positive | Xác nhận thêm qua TC_API_BVA_07 (productPrice=-1 ở API tạo sản phẩm mới cũng được chấp nhận, cùng root cause thiếu @Min/@Positive).</t>
   </si>
   <si>
     <t>Sửa sản phẩm cho phép nhập giá âm (role Manager)</t>
@@ -293,12 +290,57 @@
     <t>TC_FE_MGR_03</t>
   </si>
   <si>
-    <t>Đăng nhập Manager, sửa productPrice = -10, bấm Save</t>
-  </si>
-  <si>
     <t>Cùng root cause BUG-EMP-01, dùng chung form Edit Product</t>
   </si>
   <si>
+    <t>BUG-11</t>
+  </si>
+  <si>
+    <t>Đăng ký với password dưới 3 ký tự vẫn được chấp nhận (thiếu @Valid)</t>
+  </si>
+  <si>
+    <t>TC_API_BVA_01</t>
+  </si>
+  <si>
+    <t>Đăng ký với password = "12" (2 ký tự)</t>
+  </si>
+  <si>
+    <t>400 Bad Request (User.password có @Size(min=3))</t>
+  </si>
+  <si>
+    <t>200 OK - tài khoản vẫn được tạo</t>
+  </si>
+  <si>
+    <t>Người làm task BVA</t>
+  </si>
+  <si>
+    <t>Root cause: UserController.save() KHÔNG có @Valid trước @RequestBody User user -&gt; toàn bộ Bean Validation trên User entity (bao gồm @Size(min=3) của password) bị vô hiệu hoá hoàn toàn, không riêng gì password.</t>
+  </si>
+  <si>
+    <t>BUG-12</t>
+  </si>
+  <si>
+    <t>Thêm vào giỏ hàng với quantity=0 vẫn được chấp nhận (thiếu @Valid)</t>
+  </si>
+  <si>
+    <t>POST /cart/add</t>
+  </si>
+  <si>
+    <t>TC_API_BVA_03</t>
+  </si>
+  <si>
+    <t>Gửi {"productId": "B0001", "quantity": 0}</t>
+  </si>
+  <si>
+    <t>400 Bad Request (ItemForm.quantity có @Min(value=1))</t>
+  </si>
+  <si>
+    <t>200 OK, body true - vẫn thêm thành công</t>
+  </si>
+  <si>
+    <t>Root cause: CartController.addToCart() KHÔNG có @Valid trước @RequestBody ItemForm form -&gt; @Min(value=1) của quantity bị vô hiệu hoá. CÙNG PATTERN với BUG-11 - gợi ý kiểm tra thêm các endpoint khác có @RequestBody nhưng thiếu @Valid.</t>
+  </si>
+  <si>
     <t>HƯỚNG DẪN DÙNG FILE NÀY</t>
   </si>
   <si>
@@ -341,27 +383,35 @@
     <t xml:space="preserve">   nhưng có thể workaround) / Thấp (edge case hiếm gặp).</t>
   </si>
   <si>
-    <t xml:space="preserve">Người Fix </t>
+    <t>Đăng nhập Employee, sửa productPrice = -30, bấm Save</t>
+  </si>
+  <si>
+    <t>Đăng nhập Manager, sửa productPrice = -30, bấm Save</t>
+  </si>
+  <si>
+    <t>Thanh</t>
+  </si>
+  <si>
+    <t>Người Fix</t>
+  </si>
+  <si>
+    <t>SCRUM-43</t>
+  </si>
+  <si>
+    <t>SCRUM-44</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -373,6 +423,24 @@
       <sz val="13"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -416,16 +484,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -728,7 +799,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -744,419 +815,514 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="L1" s="1" t="s">
+      <c r="K1" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:12" ht="148.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2" t="s">
+      <c r="J4" s="5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="K4" s="5"/>
+      <c r="L4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="2" t="s">
+    </row>
+    <row r="5" spans="1:12" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="B5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="D5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="E5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="F5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="G5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="H5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2" t="s">
+      <c r="J5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="132" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="I6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="2" t="s">
+      <c r="K12" s="5"/>
+      <c r="L12" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="165" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I13" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" s="2" t="s">
+      <c r="J13" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="181.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I14" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="51" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="51" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2" t="s">
-        <v>91</v>
+      <c r="J14" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1169,79 +1335,79 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>92</v>
+      <c r="A1" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
+      <c r="A2" s="2"/>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>93</v>
+      <c r="A3" s="2" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>94</v>
+      <c r="A4" s="2" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
+      <c r="A5" s="2"/>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>95</v>
+      <c r="A6" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>96</v>
+      <c r="A7" s="2" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>97</v>
+      <c r="A8" s="2" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>98</v>
+      <c r="A9" s="2" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>99</v>
+      <c r="A10" s="2" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>100</v>
+      <c r="A11" s="2" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>101</v>
+      <c r="A12" s="2" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>102</v>
+      <c r="A13" s="2" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>103</v>
+      <c r="A14" s="2" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>104</v>
+      <c r="A15" s="2" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>105</v>
+      <c r="A16" s="2" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
